--- a/Solution_recipes/DS_SS_highSalt_Relax/DS_Relax.xlsx
+++ b/Solution_recipes/DS_SS_highSalt_Relax/DS_Relax.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atya222\Documents\GitHub\Protocols\Solution_recipes\DS_SS_Relax\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minto\Documents\GitHub\Protocols\Solution_recipes\DS_SS_highSalt_Relax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617AC473-F875-4F7A-B0B8-A90AA2D6A295}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D845E9-1694-4F2B-BA43-37EBCA6A4772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="500mL" sheetId="1" r:id="rId1"/>
-    <sheet name="250mL" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'250mL'!$A$1:$I$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'500mL'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'500mL'!$A$1:$K$16</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>Made by</t>
   </si>
@@ -42,51 +53,21 @@
     <t>Lot #</t>
   </si>
   <si>
-    <t>MW</t>
-  </si>
-  <si>
-    <t>% purity</t>
-  </si>
-  <si>
-    <t>Corrected MW</t>
-  </si>
-  <si>
-    <t>Final Conc</t>
-  </si>
-  <si>
-    <t>Amount for 250 ml</t>
-  </si>
-  <si>
-    <t>Amount added</t>
-  </si>
-  <si>
     <t>KCl</t>
   </si>
   <si>
     <t>Sigma</t>
   </si>
   <si>
-    <t>100 mM</t>
-  </si>
-  <si>
     <t>Imidazole</t>
   </si>
   <si>
-    <t>20 mM</t>
-  </si>
-  <si>
     <t>EGTA</t>
   </si>
   <si>
-    <t>2 mM</t>
-  </si>
-  <si>
     <t>ATP</t>
   </si>
   <si>
-    <t>4 mM</t>
-  </si>
-  <si>
     <t>MgCl2</t>
   </si>
   <si>
@@ -96,15 +77,9 @@
     <t>500 mM</t>
   </si>
   <si>
-    <t>7 mM</t>
-  </si>
-  <si>
     <t>14 mL</t>
   </si>
   <si>
-    <t>7 ml</t>
-  </si>
-  <si>
     <t>Initial pH</t>
   </si>
   <si>
@@ -117,35 +92,47 @@
     <t>Target pH = 7.00</t>
   </si>
   <si>
-    <t>HCl/KOH added</t>
-  </si>
-  <si>
     <t>Total HCl / KOH added</t>
   </si>
   <si>
     <t>Amount added (g)</t>
   </si>
   <si>
-    <t>Amount for
-1000mL</t>
-  </si>
-  <si>
-    <t>Amount for
+    <t>Sigma (Roche)</t>
+  </si>
+  <si>
+    <t>28 mL</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Molecular Weight (g/mol)</t>
+  </si>
+  <si>
+    <t>Purity (%)</t>
+  </si>
+  <si>
+    <t>Corrected Molecular Weight (g/mol)</t>
+  </si>
+  <si>
+    <t>Final Concentration (mM)</t>
+  </si>
+  <si>
+    <t>Amount (g) for
 500mL</t>
   </si>
   <si>
-    <t>Corrected
-MW</t>
-  </si>
-  <si>
-    <t>Sigma (Roche)</t>
-  </si>
-  <si>
-    <t>28 mL</t>
-  </si>
-  <si>
-    <t>55208291
-55208292</t>
+    <t>Amount (g) for 250mL</t>
+  </si>
+  <si>
+    <t>concentration (mM)</t>
+  </si>
+  <si>
+    <t>7 mL</t>
+  </si>
+  <si>
+    <t>Amount (g) for 1000mL</t>
   </si>
 </sst>
 </file>
@@ -192,7 +179,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -321,21 +308,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -476,6 +448,127 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -483,75 +576,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -570,41 +621,95 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -624,9 +729,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -664,7 +769,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -770,7 +875,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -912,7 +1017,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -924,222 +1029,239 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" customWidth="1"/>
+    <col min="4" max="4" width="19.36328125" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" customWidth="1"/>
+    <col min="6" max="6" width="20.453125" customWidth="1"/>
+    <col min="7" max="7" width="19.36328125" customWidth="1"/>
+    <col min="8" max="8" width="13.81640625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14.54296875" customWidth="1"/>
+    <col min="11" max="11" width="17.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:11" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="43"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="44"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="45"/>
+    </row>
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="34"/>
+      <c r="K4" s="15" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="16"/>
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="5">
+        <v>74.55</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="11" t="e">
+        <f>D5/(E5/100)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G5" s="5">
+        <v>100</v>
+      </c>
+      <c r="H5" s="10" t="e">
+        <f>I5*2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I5" s="10" t="e">
+        <f>F5*0.1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J5" s="26" t="e">
+        <f>I5/2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K5" s="6"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4"/>
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="5">
+        <v>68.08</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="11" t="e">
+        <f>D6/(E6/100)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G6" s="5">
+        <v>20</v>
+      </c>
+      <c r="H6" s="10" t="e">
+        <f>I6*2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I6" s="10" t="e">
+        <f>F6*0.02</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J6" s="26" t="e">
+        <f>I6/2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K6" s="6"/>
     </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="5">
+        <v>380.35</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="11" t="e">
+        <f>D7/(E7/100)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G7" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="29" t="s">
+      <c r="H7" s="10" t="e">
+        <f>I7*2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I7" s="10" t="e">
+        <f>F7*0.002</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J7" s="26" t="e">
+        <f>I7/2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="29">
+        <v>605.19000000000005</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32" t="e">
+        <f>D8/(E8/100)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G8" s="29">
         <v>4</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>32</v>
-      </c>
+      <c r="H8" s="33" t="e">
+        <f>I8*2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I8" s="33" t="e">
+        <f>F8*0.004</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J8" s="34" t="e">
+        <f>I8/2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K8" s="35"/>
     </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
+    <row r="9" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="C9" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="39"/>
+      <c r="F9" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19">
-        <v>74.55</v>
-      </c>
-      <c r="E5" s="19">
-        <v>99.6</v>
-      </c>
-      <c r="F5" s="27">
-        <f>D5/(E5/100)</f>
-        <v>74.849397590361448</v>
-      </c>
-      <c r="G5" s="19" t="s">
+      <c r="G9" s="37">
+        <v>7</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="26">
-        <f>I5*2</f>
-        <v>14.96987951807229</v>
-      </c>
-      <c r="I5" s="26">
-        <f>F5*0.1</f>
-        <v>7.4849397590361448</v>
-      </c>
-      <c r="J5" s="20"/>
+      <c r="J9" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="41"/>
     </row>
-    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19">
-        <v>68.08</v>
-      </c>
-      <c r="E6" s="19">
-        <v>97.9</v>
-      </c>
-      <c r="F6" s="27">
-        <f>D6/(E6/100)</f>
-        <v>69.540347293156273</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="26">
-        <f>I6*2</f>
-        <v>2.7816138917262512</v>
-      </c>
-      <c r="I6" s="26">
-        <f>F6*0.02</f>
-        <v>1.3908069458631256</v>
-      </c>
-      <c r="J6" s="20"/>
-    </row>
-    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19">
-        <v>380.35</v>
-      </c>
-      <c r="E7" s="19">
-        <v>97.9</v>
-      </c>
-      <c r="F7" s="27">
-        <f>D7/(E7/100)</f>
-        <v>388.50868232890701</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="26">
-        <f>I7*2</f>
-        <v>1.554034729315628</v>
-      </c>
-      <c r="I7" s="26">
-        <f>F7*0.002</f>
-        <v>0.77701736465781401</v>
-      </c>
-      <c r="J7" s="20"/>
-    </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="19">
-        <v>605.19000000000005</v>
-      </c>
-      <c r="E8" s="32">
-        <v>99</v>
-      </c>
-      <c r="F8" s="27">
-        <f>D8/(E8/100)</f>
-        <v>611.30303030303037</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="26">
-        <f>I8*2</f>
-        <v>4.8904242424242428</v>
-      </c>
-      <c r="I8" s="26">
-        <f>F8*0.004</f>
-        <v>2.4452121212121214</v>
-      </c>
-      <c r="J8" s="20"/>
-    </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="23"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1149,12 +1271,13 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="36"/>
+    <row r="11" spans="1:11" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="17"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1162,12 +1285,13 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="14"/>
+    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1175,282 +1299,11 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="38"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="41"/>
-      <c r="B16" s="42"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B16"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE4004A7-A1BB-405F-A924-39D6EF8FB4D0}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="34"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="16"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2">
-        <v>74.55</v>
-      </c>
-      <c r="E5" s="2">
-        <v>99.6</v>
-      </c>
-      <c r="F5" s="2">
-        <f t="shared" ref="F5:F8" si="0">D5/(E5/100)</f>
-        <v>74.849397590361448</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="2">
-        <f>F5*0.1/2</f>
-        <v>3.7424698795180724</v>
-      </c>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2">
-        <v>68.08</v>
-      </c>
-      <c r="E6" s="2">
-        <v>97.5</v>
-      </c>
-      <c r="F6" s="2">
-        <f t="shared" si="0"/>
-        <v>69.825641025641019</v>
-      </c>
-      <c r="G6" s="2" t="s">
+    <row r="13" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>15</v>
-      </c>
-      <c r="H6" s="2">
-        <f>F6*0.02/2</f>
-        <v>0.69825641025641016</v>
-      </c>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2">
-        <v>380.35</v>
-      </c>
-      <c r="E7" s="2">
-        <v>97.5</v>
-      </c>
-      <c r="F7" s="2">
-        <f t="shared" si="0"/>
-        <v>390.10256410256414</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="2">
-        <f>F7*0.002/2</f>
-        <v>0.39010256410256416</v>
-      </c>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2">
-        <v>605.20000000000005</v>
-      </c>
-      <c r="E8" s="2">
-        <v>99</v>
-      </c>
-      <c r="F8" s="2">
-        <f t="shared" si="0"/>
-        <v>611.31313131313141</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="2">
-        <f>F8*0.004/2</f>
-        <v>1.2226262626262629</v>
-      </c>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="12"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="1"/>
@@ -1460,24 +1313,43 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="12"/>
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="D14" s="42"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="22"/>
+      <c r="B16" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="D9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="91" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100965EA08FA511AE4C9FFF632E6536ED13" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abfa450e2c882fa05ec7f6a4b4016779">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5d5a2885-0f9b-4d04-9bc1-f867a2376b8a" xmlns:ns3="6cbc0c5a-d948-46e5-8624-1bad210f77c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53678093842f3275b6926b32e7a9c141" ns2:_="" ns3:_="">
     <xsd:import namespace="5d5a2885-0f9b-4d04-9bc1-f867a2376b8a"/>
@@ -1700,12 +1572,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1716,6 +1582,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33AFEA7C-ECB0-4A51-9E17-02E120CDEEE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6cbc0c5a-d948-46e5-8624-1bad210f77c7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5d5a2885-0f9b-4d04-9bc1-f867a2376b8a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A161E6A-5B3F-4912-ADEE-71AD0FF6FC00}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1734,23 +1617,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33AFEA7C-ECB0-4A51-9E17-02E120CDEEE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6cbc0c5a-d948-46e5-8624-1bad210f77c7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5d5a2885-0f9b-4d04-9bc1-f867a2376b8a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C3833AD-3BAD-44F9-A428-5312EFC8FF4F}">
   <ds:schemaRefs>
